--- a/lecturePlan.xlsx
+++ b/lecturePlan.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s15052\Documents\Teaching\BAN430\BAN430_book\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sondre/Documents/BAN430/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968059AC-57D1-4157-B576-60F787734261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62E36D0-7214-5D44-AF70-53C9F46E51B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{DEDCCCE6-C2B3-4C3C-BD8B-2E3EEC4135F8}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="19900" activeTab="3" xr2:uid="{DEDCCCE6-C2B3-4C3C-BD8B-2E3EEC4135F8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="kladd" sheetId="1" r:id="rId1"/>
+    <sheet name="v2023" sheetId="2" r:id="rId2"/>
+    <sheet name="v2024" sheetId="4" r:id="rId3"/>
+    <sheet name="h2026" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="129">
   <si>
     <t>Week number</t>
   </si>
@@ -332,10 +332,97 @@
     <t>Walmart workshop</t>
   </si>
   <si>
-    <t>Walmart solutions</t>
-  </si>
-  <si>
-    <t>No lecture: Study for exam</t>
+    <t>August</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>Monday 12:15-14:00</t>
+  </si>
+  <si>
+    <t>Wednesday 14:15-16:00</t>
+  </si>
+  <si>
+    <t>No lecture</t>
+  </si>
+  <si>
+    <t>31.08.2026</t>
+  </si>
+  <si>
+    <t>07.10.2026</t>
+  </si>
+  <si>
+    <t>12.10.2026</t>
+  </si>
+  <si>
+    <t>5-hour digital school exam</t>
+  </si>
+  <si>
+    <t>19.08.2026</t>
+  </si>
+  <si>
+    <t>17.08.2026</t>
+  </si>
+  <si>
+    <t>24.08.2026</t>
+  </si>
+  <si>
+    <t>26.08.2026</t>
+  </si>
+  <si>
+    <t>07.09.2026</t>
+  </si>
+  <si>
+    <t>09.09.2026</t>
+  </si>
+  <si>
+    <t>02.09.2026</t>
+  </si>
+  <si>
+    <t>14.09.2026</t>
+  </si>
+  <si>
+    <t>16.09.2026</t>
+  </si>
+  <si>
+    <t>21.09.2026</t>
+  </si>
+  <si>
+    <t>23.09.2026</t>
+  </si>
+  <si>
+    <t>28.09.2026</t>
+  </si>
+  <si>
+    <t>30.09.2026</t>
+  </si>
+  <si>
+    <t>05.10.2026</t>
+  </si>
+  <si>
+    <t>14.10.2026</t>
+  </si>
+  <si>
+    <t>19.10.2026</t>
+  </si>
+  <si>
+    <t>21.10.2026</t>
+  </si>
+  <si>
+    <t>26.10.2026</t>
+  </si>
+  <si>
+    <t>28.10.2026</t>
+  </si>
+  <si>
+    <t>02.11.2026</t>
+  </si>
+  <si>
+    <t>24.11.2026</t>
+  </si>
+  <si>
+    <t>Oktober</t>
   </si>
 </sst>
 </file>
@@ -800,10 +887,39 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,9 +932,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -851,30 +964,6 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -896,9 +985,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-tema">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -936,7 +1025,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1042,7 +1131,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1193,16 +1282,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1602BAC1-380E-4833-8006-FA92A91C8286}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="33.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1222,7 +1311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3</v>
       </c>
@@ -1242,7 +1331,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>4</v>
       </c>
@@ -1256,7 +1345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5</v>
       </c>
@@ -1270,7 +1359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>6</v>
       </c>
@@ -1284,7 +1373,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>7</v>
       </c>
@@ -1301,7 +1390,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>8</v>
       </c>
@@ -1315,7 +1404,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>9</v>
       </c>
@@ -1329,7 +1418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10</v>
       </c>
@@ -1340,7 +1429,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>11</v>
       </c>
@@ -1354,7 +1443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>12</v>
       </c>
@@ -1368,7 +1457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>13</v>
       </c>
@@ -1385,7 +1474,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>14</v>
       </c>
@@ -1396,7 +1485,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>15</v>
       </c>
@@ -1417,18 +1506,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6C382B-A390-441B-AFA9-C1DFECC0D308}">
   <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" customWidth="1"/>
-    <col min="4" max="4" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
+    <col min="6" max="6" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1454,7 +1543,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3</v>
       </c>
@@ -1480,7 +1569,7 @@
         <v>44945</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>4</v>
       </c>
@@ -1500,7 +1589,7 @@
         <v>44952</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5</v>
       </c>
@@ -1523,7 +1612,7 @@
         <v>44959</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>6</v>
       </c>
@@ -1546,7 +1635,7 @@
         <v>44966</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>8</v>
       </c>
@@ -1569,7 +1658,7 @@
         <v>44973</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>7</v>
       </c>
@@ -1592,7 +1681,7 @@
         <v>44980</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>9</v>
       </c>
@@ -1612,7 +1701,7 @@
         <v>44987</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10</v>
       </c>
@@ -1632,7 +1721,7 @@
         <v>44994</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>11</v>
       </c>
@@ -1652,7 +1741,7 @@
         <v>45001</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>12</v>
       </c>
@@ -1675,7 +1764,7 @@
         <v>45008</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>13</v>
       </c>
@@ -1698,7 +1787,7 @@
         <v>45015</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>14</v>
       </c>
@@ -1715,7 +1804,7 @@
         <v>45022</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>15</v>
       </c>
@@ -1732,15 +1821,15 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G15" s="2"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G16" s="2"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="32" t="s">
         <v>47</v>
       </c>
@@ -1751,8 +1840,8 @@
       <c r="G17" s="7"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="85" t="s">
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="93" t="s">
         <v>54</v>
       </c>
       <c r="B18" s="23">
@@ -1763,8 +1852,8 @@
       </c>
       <c r="D18" s="39"/>
     </row>
-    <row r="19" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="86"/>
+    <row r="19" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="94"/>
       <c r="B19" s="26" t="s">
         <v>40</v>
       </c>
@@ -1773,8 +1862,8 @@
       </c>
       <c r="D19" s="40"/>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="86"/>
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="94"/>
       <c r="B20" s="23">
         <v>44949</v>
       </c>
@@ -1783,8 +1872,8 @@
       </c>
       <c r="D20" s="39"/>
     </row>
-    <row r="21" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+    <row r="21" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="94"/>
       <c r="B21" s="26" t="s">
         <v>3</v>
       </c>
@@ -1793,8 +1882,8 @@
       </c>
       <c r="D21" s="40"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="94"/>
       <c r="B22" s="23">
         <v>44956</v>
       </c>
@@ -1803,8 +1892,8 @@
       </c>
       <c r="D22" s="39"/>
     </row>
-    <row r="23" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="87"/>
+    <row r="23" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="95"/>
       <c r="B23" s="26" t="s">
         <v>7</v>
       </c>
@@ -1813,8 +1902,8 @@
       </c>
       <c r="D23" s="40"/>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="85" t="s">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="93" t="s">
         <v>55</v>
       </c>
       <c r="B24" s="25">
@@ -1825,8 +1914,8 @@
       </c>
       <c r="D24" s="39"/>
     </row>
-    <row r="25" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+    <row r="25" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="94"/>
       <c r="B25" s="24" t="s">
         <v>8</v>
       </c>
@@ -1835,8 +1924,8 @@
       </c>
       <c r="D25" s="40"/>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="86"/>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="94"/>
       <c r="B26" s="23">
         <v>44970</v>
       </c>
@@ -1845,8 +1934,8 @@
       </c>
       <c r="D26" s="39"/>
     </row>
-    <row r="27" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86"/>
+    <row r="27" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="94"/>
       <c r="B27" s="26" t="s">
         <v>42</v>
       </c>
@@ -1855,8 +1944,8 @@
       </c>
       <c r="D27" s="40"/>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="94"/>
       <c r="B28" s="19">
         <v>44977</v>
       </c>
@@ -1865,8 +1954,8 @@
       </c>
       <c r="D28" s="39"/>
     </row>
-    <row r="29" spans="1:8" s="5" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
+    <row r="29" spans="1:8" s="5" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="94"/>
       <c r="B29" s="36" t="s">
         <v>59</v>
       </c>
@@ -1875,8 +1964,8 @@
       </c>
       <c r="D29" s="40"/>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="86"/>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="94"/>
       <c r="B30" s="9">
         <v>44984</v>
       </c>
@@ -1885,8 +1974,8 @@
       </c>
       <c r="D30" s="39"/>
     </row>
-    <row r="31" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="87"/>
+    <row r="31" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="95"/>
       <c r="B31" s="10" t="s">
         <v>43</v>
       </c>
@@ -1895,8 +1984,8 @@
       </c>
       <c r="D31" s="40"/>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="85" t="s">
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="93" t="s">
         <v>56</v>
       </c>
       <c r="B32" s="11">
@@ -1907,8 +1996,8 @@
       </c>
       <c r="D32" s="39"/>
     </row>
-    <row r="33" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="86"/>
+    <row r="33" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="94"/>
       <c r="B33" s="10" t="s">
         <v>43</v>
       </c>
@@ -1917,8 +2006,8 @@
       </c>
       <c r="D33" s="40"/>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="86"/>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="94"/>
       <c r="B34" s="9">
         <v>44998</v>
       </c>
@@ -1927,8 +2016,8 @@
       </c>
       <c r="D34" s="39"/>
     </row>
-    <row r="35" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="86"/>
+    <row r="35" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="94"/>
       <c r="B35" s="10" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2026,8 @@
       </c>
       <c r="D35" s="40"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="86"/>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="94"/>
       <c r="B36" s="15">
         <v>45005</v>
       </c>
@@ -1947,8 +2036,8 @@
       </c>
       <c r="D36" s="39"/>
     </row>
-    <row r="37" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="86"/>
+    <row r="37" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="94"/>
       <c r="B37" s="16" t="s">
         <v>46</v>
       </c>
@@ -1957,8 +2046,8 @@
       </c>
       <c r="D37" s="40"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="86"/>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="94"/>
       <c r="B38" s="18">
         <v>45012</v>
       </c>
@@ -1967,8 +2056,8 @@
       </c>
       <c r="D38" s="39"/>
     </row>
-    <row r="39" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="87"/>
+    <row r="39" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="95"/>
       <c r="B39" s="17" t="s">
         <v>11</v>
       </c>
@@ -1977,8 +2066,8 @@
       </c>
       <c r="D39" s="40"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="85" t="s">
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="93" t="s">
         <v>57</v>
       </c>
       <c r="B40" s="33">
@@ -1989,16 +2078,16 @@
       </c>
       <c r="D40" s="39"/>
     </row>
-    <row r="41" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="86"/>
+    <row r="41" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="94"/>
       <c r="B41" s="34"/>
       <c r="C41" s="22" t="s">
         <v>44</v>
       </c>
       <c r="D41" s="40"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="86"/>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="94"/>
       <c r="B42" s="14">
         <v>45026</v>
       </c>
@@ -2007,8 +2096,8 @@
       </c>
       <c r="D42" s="39"/>
     </row>
-    <row r="43" spans="1:4" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="86"/>
+    <row r="43" spans="1:4" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="94"/>
       <c r="B43" s="35" t="s">
         <v>44</v>
       </c>
@@ -2017,51 +2106,51 @@
       </c>
       <c r="D43" s="40"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="86"/>
-      <c r="B44" s="88" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="94"/>
+      <c r="B44" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="89"/>
+      <c r="C44" s="97"/>
       <c r="D44" s="39"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="86"/>
-      <c r="B45" s="90"/>
-      <c r="C45" s="91"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="94"/>
+      <c r="B45" s="98"/>
+      <c r="C45" s="99"/>
       <c r="D45" s="39"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="87"/>
-      <c r="B46" s="92"/>
-      <c r="C46" s="93"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="95"/>
+      <c r="B46" s="100"/>
+      <c r="C46" s="101"/>
       <c r="D46" s="39"/>
     </row>
-    <row r="47" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="79" t="s">
+    <row r="47" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="83">
+      <c r="B47" s="79">
         <v>45054</v>
       </c>
-      <c r="C47" s="84"/>
+      <c r="C47" s="92"/>
       <c r="D47" s="39"/>
     </row>
-    <row r="48" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="80"/>
-      <c r="B48" s="81" t="s">
+    <row r="48" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="89"/>
+      <c r="B48" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="C48" s="82"/>
+      <c r="C48" s="91"/>
       <c r="D48" s="39"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="41"/>
       <c r="B49" s="41"/>
       <c r="C49" s="41"/>
       <c r="D49" s="41"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
@@ -2084,16 +2173,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C02AE7A-CD84-44B4-BCAE-299F3ABE620B}">
-  <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A780E3C1-B692-48F8-988B-66A9EFA8823C}">
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="54"/>
       <c r="B1" s="55" t="s">
         <v>93</v>
@@ -2102,8 +2190,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="98" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="83" t="s">
         <v>54</v>
       </c>
       <c r="B2" s="59" t="s">
@@ -2113,17 +2201,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="99"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="84"/>
       <c r="B3" s="42" t="s">
         <v>61</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="99"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="84"/>
       <c r="B4" s="59" t="s">
         <v>69</v>
       </c>
@@ -2131,17 +2219,17 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="99"/>
-      <c r="B5" s="44" t="s">
-        <v>4</v>
+    <row r="5" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="84"/>
+      <c r="B5" s="42" t="s">
+        <v>3</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="99"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="84"/>
       <c r="B6" s="59" t="s">
         <v>71</v>
       </c>
@@ -2149,8 +2237,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="85"/>
       <c r="B7" s="42" t="s">
         <v>7</v>
       </c>
@@ -2158,8 +2246,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="98" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="83" t="s">
         <v>55</v>
       </c>
       <c r="B8" s="61" t="s">
@@ -2169,8 +2257,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="99"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="84"/>
       <c r="B9" s="45" t="s">
         <v>8</v>
       </c>
@@ -2178,8 +2266,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="99"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="84"/>
       <c r="B10" s="59" t="s">
         <v>75</v>
       </c>
@@ -2187,8 +2275,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="99"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="84"/>
       <c r="B11" s="42" t="s">
         <v>42</v>
       </c>
@@ -2196,44 +2284,44 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="99"/>
-      <c r="B12" s="65" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="84"/>
+      <c r="B12" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="64" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="99"/>
-      <c r="B13" s="76" t="s">
+    <row r="13" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="84"/>
+      <c r="B13" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="84"/>
+      <c r="B14" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="85"/>
+      <c r="B15" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="76" t="s">
+      <c r="C15" s="49" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="99"/>
-      <c r="B14" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="100"/>
-      <c r="B15" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="77" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="98" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="83" t="s">
         <v>56</v>
       </c>
       <c r="B16" s="75" t="s">
@@ -2243,8 +2331,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="99"/>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="84"/>
       <c r="B17" s="50" t="s">
         <v>50</v>
       </c>
@@ -2252,8 +2340,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="99"/>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="84"/>
       <c r="B18" s="65" t="s">
         <v>81</v>
       </c>
@@ -2261,17 +2349,17 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="99"/>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="84"/>
       <c r="B19" s="48" t="s">
         <v>64</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="99"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="84"/>
       <c r="B20" s="68" t="s">
         <v>86</v>
       </c>
@@ -2279,17 +2367,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="99"/>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="84"/>
       <c r="B21" s="51" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="C21" s="74" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="99"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="84"/>
       <c r="B22" s="69" t="s">
         <v>88</v>
       </c>
@@ -2297,17 +2385,17 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="100"/>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="85"/>
       <c r="B23" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="78" t="s">
+      <c r="C23" s="71" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="98" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="83" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="72" t="s">
@@ -2317,17 +2405,17 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="99"/>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="84"/>
       <c r="B25" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="48" t="s">
+      <c r="C25" s="52" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="99"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="84"/>
       <c r="B26" s="66" t="s">
         <v>92</v>
       </c>
@@ -2335,347 +2423,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
-      <c r="B27" s="53" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="99"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="84"/>
+      <c r="B27" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="84"/>
       <c r="B28" s="57" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="58"/>
     </row>
-    <row r="29" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="101"/>
-      <c r="B29" s="94" t="s">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="86"/>
+      <c r="B29" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="95"/>
-    </row>
-    <row r="30" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="102"/>
-      <c r="B30" s="96" t="s">
+      <c r="C29" s="80"/>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="87"/>
+      <c r="B30" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="97"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A15"/>
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="A29:A30"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A780E3C1-B692-48F8-988B-66A9EFA8823C}">
-  <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="54"/>
-      <c r="B1" s="55" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="98" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="99"/>
-      <c r="B3" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="99"/>
-      <c r="B4" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="60" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="99"/>
-      <c r="B5" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="99"/>
-      <c r="B6" s="59" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
-      <c r="B7" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="98" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="62" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="99"/>
-      <c r="B9" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="99"/>
-      <c r="B10" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="99"/>
-      <c r="B11" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="99"/>
-      <c r="B12" s="63" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="99"/>
-      <c r="B13" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="99"/>
-      <c r="B14" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="100"/>
-      <c r="B15" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="98" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="75" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="65" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="99"/>
-      <c r="B17" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="99"/>
-      <c r="B18" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="66" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="99"/>
-      <c r="B19" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="99"/>
-      <c r="B20" s="68" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="99"/>
-      <c r="B21" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="99"/>
-      <c r="B22" s="69" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="63" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="100"/>
-      <c r="B23" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="71" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="72" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="73" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="99"/>
-      <c r="B25" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="99"/>
-      <c r="B26" s="66" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="67" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
-      <c r="B27" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="99"/>
-      <c r="B28" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="58"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="101"/>
-      <c r="B29" s="94" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="95"/>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="102"/>
-      <c r="B30" s="96" t="s">
+      <c r="C30" s="82"/>
+    </row>
+    <row r="31" spans="1:3" ht="19" x14ac:dyDescent="0.2">
+      <c r="A31" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="79">
+        <v>45054</v>
+      </c>
+      <c r="C31" s="92"/>
+    </row>
+    <row r="32" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+      <c r="A32" s="89"/>
+      <c r="B32" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="97"/>
-    </row>
-    <row r="31" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="79" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="83">
-        <v>45054</v>
-      </c>
-      <c r="C31" s="84"/>
-    </row>
-    <row r="32" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="80"/>
-      <c r="B32" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="82"/>
+      <c r="C32" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2692,4 +2484,278 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C02AE7A-CD84-44B4-BCAE-299F3ABE620B}">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="54"/>
+      <c r="B1" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="84"/>
+      <c r="B3" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="84"/>
+      <c r="B4" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="84"/>
+      <c r="B5" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="84"/>
+      <c r="B6" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="85"/>
+      <c r="B7" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="62" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="84"/>
+      <c r="B9" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="84"/>
+      <c r="B10" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="84"/>
+      <c r="B11" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="84"/>
+      <c r="B12" s="65" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="66" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="84"/>
+      <c r="B13" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="84"/>
+      <c r="B14" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="85"/>
+      <c r="B15" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="83" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="65" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="84"/>
+      <c r="B17" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="84"/>
+      <c r="B18" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="66" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="84"/>
+      <c r="B19" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="84"/>
+      <c r="B20" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="65" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="84"/>
+      <c r="B21" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="84"/>
+      <c r="B22" s="78" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="84"/>
+      <c r="B23" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="84"/>
+      <c r="B24" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="67"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="85"/>
+      <c r="B25" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="53"/>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="77"/>
+      <c r="B26" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="58"/>
+    </row>
+    <row r="27" spans="1:3" ht="19" x14ac:dyDescent="0.2">
+      <c r="A27" s="86"/>
+      <c r="B27" s="102" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="80"/>
+    </row>
+    <row r="28" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+      <c r="A28" s="87"/>
+      <c r="B28" s="81" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="82"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A8:A15"/>
+    <mergeCell ref="A16:A25"/>
+    <mergeCell ref="A27:A28"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/lecturePlan.xlsx
+++ b/lecturePlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sondre/Documents/BAN430/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62E36D0-7214-5D44-AF70-53C9F46E51B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BF5C6D-C4F2-884B-9EA4-D2465A89B79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="19900" activeTab="3" xr2:uid="{DEDCCCE6-C2B3-4C3C-BD8B-2E3EEC4135F8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="34560" windowHeight="19800" activeTab="3" xr2:uid="{DEDCCCE6-C2B3-4C3C-BD8B-2E3EEC4135F8}"/>
   </bookViews>
   <sheets>
     <sheet name="kladd" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="130">
   <si>
     <t>Week number</t>
   </si>
@@ -329,9 +329,6 @@
     <t>Summary lecture / old exam</t>
   </si>
   <si>
-    <t>Walmart workshop</t>
-  </si>
-  <si>
     <t>August</t>
   </si>
   <si>
@@ -419,10 +416,16 @@
     <t>02.11.2026</t>
   </si>
   <si>
-    <t>24.11.2026</t>
-  </si>
-  <si>
     <t>Oktober</t>
+  </si>
+  <si>
+    <t></t>
+  </si>
+  <si>
+    <t>Time series decomoposition</t>
+  </si>
+  <si>
+    <t>Dynamic regression models</t>
   </si>
 </sst>
 </file>
@@ -893,45 +896,48 @@
     <xf numFmtId="49" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -960,9 +966,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1841,7 +1844,7 @@
       <c r="H17" s="8"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="93" t="s">
+      <c r="A18" s="94" t="s">
         <v>54</v>
       </c>
       <c r="B18" s="23">
@@ -1853,7 +1856,7 @@
       <c r="D18" s="39"/>
     </row>
     <row r="19" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="94"/>
+      <c r="A19" s="95"/>
       <c r="B19" s="26" t="s">
         <v>40</v>
       </c>
@@ -1863,7 +1866,7 @@
       <c r="D19" s="40"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="94"/>
+      <c r="A20" s="95"/>
       <c r="B20" s="23">
         <v>44949</v>
       </c>
@@ -1873,7 +1876,7 @@
       <c r="D20" s="39"/>
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="94"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="26" t="s">
         <v>3</v>
       </c>
@@ -1883,7 +1886,7 @@
       <c r="D21" s="40"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="94"/>
+      <c r="A22" s="95"/>
       <c r="B22" s="23">
         <v>44956</v>
       </c>
@@ -1893,7 +1896,7 @@
       <c r="D22" s="39"/>
     </row>
     <row r="23" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="95"/>
+      <c r="A23" s="96"/>
       <c r="B23" s="26" t="s">
         <v>7</v>
       </c>
@@ -1903,7 +1906,7 @@
       <c r="D23" s="40"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B24" s="25">
@@ -1915,7 +1918,7 @@
       <c r="D24" s="39"/>
     </row>
     <row r="25" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="94"/>
+      <c r="A25" s="95"/>
       <c r="B25" s="24" t="s">
         <v>8</v>
       </c>
@@ -1925,7 +1928,7 @@
       <c r="D25" s="40"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="94"/>
+      <c r="A26" s="95"/>
       <c r="B26" s="23">
         <v>44970</v>
       </c>
@@ -1935,7 +1938,7 @@
       <c r="D26" s="39"/>
     </row>
     <row r="27" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="94"/>
+      <c r="A27" s="95"/>
       <c r="B27" s="26" t="s">
         <v>42</v>
       </c>
@@ -1945,7 +1948,7 @@
       <c r="D27" s="40"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="94"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="19">
         <v>44977</v>
       </c>
@@ -1955,7 +1958,7 @@
       <c r="D28" s="39"/>
     </row>
     <row r="29" spans="1:8" s="5" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="94"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="36" t="s">
         <v>59</v>
       </c>
@@ -1965,7 +1968,7 @@
       <c r="D29" s="40"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="94"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="9">
         <v>44984</v>
       </c>
@@ -1975,7 +1978,7 @@
       <c r="D30" s="39"/>
     </row>
     <row r="31" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="95"/>
+      <c r="A31" s="96"/>
       <c r="B31" s="10" t="s">
         <v>43</v>
       </c>
@@ -1985,7 +1988,7 @@
       <c r="D31" s="40"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="93" t="s">
+      <c r="A32" s="94" t="s">
         <v>56</v>
       </c>
       <c r="B32" s="11">
@@ -1997,7 +2000,7 @@
       <c r="D32" s="39"/>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="94"/>
+      <c r="A33" s="95"/>
       <c r="B33" s="10" t="s">
         <v>43</v>
       </c>
@@ -2007,7 +2010,7 @@
       <c r="D33" s="40"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="94"/>
+      <c r="A34" s="95"/>
       <c r="B34" s="9">
         <v>44998</v>
       </c>
@@ -2017,7 +2020,7 @@
       <c r="D34" s="39"/>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="94"/>
+      <c r="A35" s="95"/>
       <c r="B35" s="10" t="s">
         <v>43</v>
       </c>
@@ -2027,7 +2030,7 @@
       <c r="D35" s="40"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="94"/>
+      <c r="A36" s="95"/>
       <c r="B36" s="15">
         <v>45005</v>
       </c>
@@ -2037,7 +2040,7 @@
       <c r="D36" s="39"/>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="94"/>
+      <c r="A37" s="95"/>
       <c r="B37" s="16" t="s">
         <v>46</v>
       </c>
@@ -2047,7 +2050,7 @@
       <c r="D37" s="40"/>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="94"/>
+      <c r="A38" s="95"/>
       <c r="B38" s="18">
         <v>45012</v>
       </c>
@@ -2057,7 +2060,7 @@
       <c r="D38" s="39"/>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="95"/>
+      <c r="A39" s="96"/>
       <c r="B39" s="17" t="s">
         <v>11</v>
       </c>
@@ -2067,7 +2070,7 @@
       <c r="D39" s="40"/>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="93" t="s">
+      <c r="A40" s="94" t="s">
         <v>57</v>
       </c>
       <c r="B40" s="33">
@@ -2079,7 +2082,7 @@
       <c r="D40" s="39"/>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="94"/>
+      <c r="A41" s="95"/>
       <c r="B41" s="34"/>
       <c r="C41" s="22" t="s">
         <v>44</v>
@@ -2087,7 +2090,7 @@
       <c r="D41" s="40"/>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="94"/>
+      <c r="A42" s="95"/>
       <c r="B42" s="14">
         <v>45026</v>
       </c>
@@ -2097,7 +2100,7 @@
       <c r="D42" s="39"/>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="94"/>
+      <c r="A43" s="95"/>
       <c r="B43" s="35" t="s">
         <v>44</v>
       </c>
@@ -2107,33 +2110,33 @@
       <c r="D43" s="40"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="94"/>
-      <c r="B44" s="96" t="s">
+      <c r="A44" s="95"/>
+      <c r="B44" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="97"/>
+      <c r="C44" s="98"/>
       <c r="D44" s="39"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="94"/>
-      <c r="B45" s="98"/>
-      <c r="C45" s="99"/>
+      <c r="A45" s="95"/>
+      <c r="B45" s="99"/>
+      <c r="C45" s="100"/>
       <c r="D45" s="39"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="95"/>
-      <c r="B46" s="100"/>
-      <c r="C46" s="101"/>
+      <c r="A46" s="96"/>
+      <c r="B46" s="101"/>
+      <c r="C46" s="102"/>
       <c r="D46" s="39"/>
     </row>
     <row r="47" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="79">
+      <c r="B47" s="92">
         <v>45054</v>
       </c>
-      <c r="C47" s="92"/>
+      <c r="C47" s="93"/>
       <c r="D47" s="39"/>
     </row>
     <row r="48" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2441,7 +2444,7 @@
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="86"/>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="79" t="s">
         <v>94</v>
       </c>
       <c r="C29" s="80"/>
@@ -2457,10 +2460,10 @@
       <c r="A31" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="79">
+      <c r="B31" s="92">
         <v>45054</v>
       </c>
-      <c r="C31" s="92"/>
+      <c r="C31" s="93"/>
     </row>
     <row r="32" spans="1:3" ht="24" x14ac:dyDescent="0.2">
       <c r="A32" s="89"/>
@@ -2491,7 +2494,6 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
@@ -2501,21 +2503,21 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="54"/>
       <c r="B1" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="56" t="s">
         <v>100</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="83" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" s="60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2524,16 +2526,16 @@
         <v>61</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="84"/>
       <c r="B4" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="60" t="s">
         <v>109</v>
-      </c>
-      <c r="C4" s="60" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -2542,16 +2544,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="84"/>
       <c r="B6" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="60" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -2560,18 +2562,18 @@
         <v>4</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="83" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B8" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="62" t="s">
         <v>111</v>
-      </c>
-      <c r="C8" s="62" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2580,16 +2582,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="84"/>
       <c r="B10" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="60" t="s">
         <v>114</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2598,16 +2600,16 @@
         <v>8</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="84"/>
       <c r="B12" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="66" t="s">
         <v>116</v>
-      </c>
-      <c r="C12" s="66" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -2616,36 +2618,36 @@
         <v>42</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="84"/>
       <c r="B14" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="66" t="s">
         <v>118</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="85"/>
       <c r="B15" s="76" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C15" s="76" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="83" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" s="67" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2654,52 +2656,52 @@
         <v>43</v>
       </c>
       <c r="C17" s="48" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="84"/>
       <c r="B18" s="65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" s="66" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="84"/>
-      <c r="B19" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>97</v>
+      <c r="B19" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="84"/>
       <c r="B20" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="65" t="s">
         <v>122</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="84"/>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="48" t="s">
-        <v>11</v>
+      <c r="C21" s="49" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="84"/>
       <c r="B22" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="65" t="s">
         <v>124</v>
-      </c>
-      <c r="C22" s="65" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2714,7 +2716,7 @@
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="84"/>
       <c r="B24" s="68" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C24" s="67"/>
     </row>
@@ -2734,7 +2736,7 @@
     </row>
     <row r="27" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="86"/>
-      <c r="B27" s="102" t="s">
+      <c r="B27" s="79" t="s">
         <v>127</v>
       </c>
       <c r="C27" s="80"/>
@@ -2742,7 +2744,7 @@
     <row r="28" spans="1:3" ht="24" x14ac:dyDescent="0.2">
       <c r="A28" s="87"/>
       <c r="B28" s="81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C28" s="82"/>
     </row>
